--- a/demo-excel/07-Pipeline-Forecast-Penjualan-demo.xlsx
+++ b/demo-excel/07-Pipeline-Forecast-Penjualan-demo.xlsx
@@ -11,9 +11,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PARAMETER" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEAL" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RINGKASAN" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FULL-PER_SALES" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FULL-FORECAST" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FULL-DASHBOARD" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DEAL'!$A$5:$L$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DEAL'!$A$5:$L$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,7 +31,7 @@
     <numFmt numFmtId="167" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -105,6 +108,29 @@
       <color rgb="00B9770E"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000B1A30"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="0033445C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001E8449"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -165,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -241,6 +267,12 @@
     <xf numFmtId="168" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -771,7 +803,7 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Daftar peluang penjualan (kapasitas 60 baris): nilai, tahap, tanggal, probabilitas otomatis, umur, dan status.</t>
+          <t>Daftar peluang penjualan (kapasitas 30 baris): nilai, tahap, tanggal, probabilitas otomatis, umur, dan status.</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1152,7 +1184,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Kapasitas 60 baris</t>
+          <t>Kapasitas 30 baris</t>
         </is>
       </c>
     </row>
@@ -2266,40 +2298,14 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="23" t="inlineStr">
-        <is>
-          <t>D-021</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>CV Citra Warna</t>
-        </is>
-      </c>
-      <c r="C26" s="23" t="inlineStr">
-        <is>
-          <t>Sekar Wulandari</t>
-        </is>
-      </c>
-      <c r="D26" s="23" t="inlineStr">
-        <is>
-          <t>Media Sosial</t>
-        </is>
-      </c>
-      <c r="E26" s="23" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="F26" s="24" t="n">
-        <v>101000000</v>
-      </c>
-      <c r="G26" s="25" t="n">
-        <v>46262</v>
-      </c>
-      <c r="H26" s="25" t="n">
-        <v>46430</v>
-      </c>
+      <c r="A26" s="23" t="n"/>
+      <c r="B26" s="23" t="n"/>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="23" t="n"/>
+      <c r="F26" s="24" t="n"/>
+      <c r="G26" s="25" t="n"/>
+      <c r="H26" s="25" t="n"/>
       <c r="I26" s="26">
         <f>IF(E26="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E26,PARAMETER!$B$9:$B$14,0)),0))</f>
         <v/>
@@ -2318,40 +2324,14 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="inlineStr">
-        <is>
-          <t>D-022</t>
-        </is>
-      </c>
-      <c r="B27" s="23" t="inlineStr">
-        <is>
-          <t>CV Berkah Sentosa</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="inlineStr">
-        <is>
-          <t>Rina Pratama</t>
-        </is>
-      </c>
-      <c r="D27" s="23" t="inlineStr">
-        <is>
-          <t>Pameran</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="F27" s="24" t="n">
-        <v>214000000</v>
-      </c>
-      <c r="G27" s="25" t="n">
-        <v>46246</v>
-      </c>
-      <c r="H27" s="25" t="n">
-        <v>46451</v>
-      </c>
+      <c r="A27" s="23" t="n"/>
+      <c r="B27" s="23" t="n"/>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="23" t="n"/>
+      <c r="F27" s="24" t="n"/>
+      <c r="G27" s="25" t="n"/>
+      <c r="H27" s="25" t="n"/>
       <c r="I27" s="26">
         <f>IF(E27="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E27,PARAMETER!$B$9:$B$14,0)),0))</f>
         <v/>
@@ -2370,40 +2350,14 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="inlineStr">
-        <is>
-          <t>D-023</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
-        <is>
-          <t>CV Mitra Abadi</t>
-        </is>
-      </c>
-      <c r="C28" s="23" t="inlineStr">
-        <is>
-          <t>Sekar Wulandari</t>
-        </is>
-      </c>
-      <c r="D28" s="23" t="inlineStr">
-        <is>
-          <t>Referral</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="inlineStr">
-        <is>
-          <t>Menang</t>
-        </is>
-      </c>
-      <c r="F28" s="24" t="n">
-        <v>39000000</v>
-      </c>
-      <c r="G28" s="25" t="n">
-        <v>46274</v>
-      </c>
-      <c r="H28" s="25" t="n">
-        <v>46307</v>
-      </c>
+      <c r="A28" s="23" t="n"/>
+      <c r="B28" s="23" t="n"/>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="23" t="n"/>
+      <c r="F28" s="24" t="n"/>
+      <c r="G28" s="25" t="n"/>
+      <c r="H28" s="25" t="n"/>
       <c r="I28" s="26">
         <f>IF(E28="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E28,PARAMETER!$B$9:$B$14,0)),0))</f>
         <v/>
@@ -2422,40 +2376,14 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
-        <is>
-          <t>D-024</t>
-        </is>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>PT Sinar Baru</t>
-        </is>
-      </c>
-      <c r="C29" s="23" t="inlineStr">
-        <is>
-          <t>Sekar Wulandari</t>
-        </is>
-      </c>
-      <c r="D29" s="23" t="inlineStr">
-        <is>
-          <t>Pameran</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
-        <is>
-          <t>Menang</t>
-        </is>
-      </c>
-      <c r="F29" s="24" t="n">
-        <v>27000000</v>
-      </c>
-      <c r="G29" s="25" t="n">
-        <v>46161</v>
-      </c>
-      <c r="H29" s="25" t="n">
-        <v>46198</v>
-      </c>
+      <c r="A29" s="23" t="n"/>
+      <c r="B29" s="23" t="n"/>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="24" t="n"/>
+      <c r="G29" s="25" t="n"/>
+      <c r="H29" s="25" t="n"/>
       <c r="I29" s="26">
         <f>IF(E29="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E29,PARAMETER!$B$9:$B$14,0)),0))</f>
         <v/>
@@ -2474,40 +2402,14 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="23" t="inlineStr">
-        <is>
-          <t>D-025</t>
-        </is>
-      </c>
-      <c r="B30" s="23" t="inlineStr">
-        <is>
-          <t>PT Cahaya Prima</t>
-        </is>
-      </c>
-      <c r="C30" s="23" t="inlineStr">
-        <is>
-          <t>Dimas Anggoro</t>
-        </is>
-      </c>
-      <c r="D30" s="23" t="inlineStr">
-        <is>
-          <t>Cold Call</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="inlineStr">
-        <is>
-          <t>Prospek</t>
-        </is>
-      </c>
-      <c r="F30" s="24" t="n">
-        <v>158000000</v>
-      </c>
-      <c r="G30" s="25" t="n">
-        <v>46179</v>
-      </c>
-      <c r="H30" s="25" t="n">
-        <v>46384</v>
-      </c>
+      <c r="A30" s="23" t="n"/>
+      <c r="B30" s="23" t="n"/>
+      <c r="C30" s="23" t="n"/>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="24" t="n"/>
+      <c r="G30" s="25" t="n"/>
+      <c r="H30" s="25" t="n"/>
       <c r="I30" s="26">
         <f>IF(E30="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E30,PARAMETER!$B$9:$B$14,0)),0))</f>
         <v/>
@@ -2526,40 +2428,14 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="inlineStr">
-        <is>
-          <t>D-026</t>
-        </is>
-      </c>
-      <c r="B31" s="23" t="inlineStr">
-        <is>
-          <t>CV Citra Warna</t>
-        </is>
-      </c>
-      <c r="C31" s="23" t="inlineStr">
-        <is>
-          <t>Sekar Wulandari</t>
-        </is>
-      </c>
-      <c r="D31" s="23" t="inlineStr">
-        <is>
-          <t>Referral</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="inlineStr">
-        <is>
-          <t>Menang</t>
-        </is>
-      </c>
-      <c r="F31" s="24" t="n">
-        <v>16000000</v>
-      </c>
-      <c r="G31" s="25" t="n">
-        <v>46123</v>
-      </c>
-      <c r="H31" s="25" t="n">
-        <v>46174</v>
-      </c>
+      <c r="A31" s="23" t="n"/>
+      <c r="B31" s="23" t="n"/>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="23" t="n"/>
+      <c r="F31" s="24" t="n"/>
+      <c r="G31" s="25" t="n"/>
+      <c r="H31" s="25" t="n"/>
       <c r="I31" s="26">
         <f>IF(E31="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E31,PARAMETER!$B$9:$B$14,0)),0))</f>
         <v/>
@@ -2578,40 +2454,14 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="23" t="inlineStr">
-        <is>
-          <t>D-027</t>
-        </is>
-      </c>
-      <c r="B32" s="23" t="inlineStr">
-        <is>
-          <t>CV Mitra Abadi</t>
-        </is>
-      </c>
-      <c r="C32" s="23" t="inlineStr">
-        <is>
-          <t>Sekar Wulandari</t>
-        </is>
-      </c>
-      <c r="D32" s="23" t="inlineStr">
-        <is>
-          <t>Pameran</t>
-        </is>
-      </c>
-      <c r="E32" s="23" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="F32" s="24" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="G32" s="25" t="n">
-        <v>46283</v>
-      </c>
-      <c r="H32" s="25" t="n">
-        <v>46340</v>
-      </c>
+      <c r="A32" s="23" t="n"/>
+      <c r="B32" s="23" t="n"/>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="23" t="n"/>
+      <c r="E32" s="23" t="n"/>
+      <c r="F32" s="24" t="n"/>
+      <c r="G32" s="25" t="n"/>
+      <c r="H32" s="25" t="n"/>
       <c r="I32" s="26">
         <f>IF(E32="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E32,PARAMETER!$B$9:$B$14,0)),0))</f>
         <v/>
@@ -2630,40 +2480,14 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="23" t="inlineStr">
-        <is>
-          <t>D-028</t>
-        </is>
-      </c>
-      <c r="B33" s="23" t="inlineStr">
-        <is>
-          <t>CV Mitra Abadi</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="inlineStr">
-        <is>
-          <t>Sekar Wulandari</t>
-        </is>
-      </c>
-      <c r="D33" s="23" t="inlineStr">
-        <is>
-          <t>Mitra</t>
-        </is>
-      </c>
-      <c r="E33" s="23" t="inlineStr">
-        <is>
-          <t>Menang</t>
-        </is>
-      </c>
-      <c r="F33" s="24" t="n">
-        <v>42000000</v>
-      </c>
-      <c r="G33" s="25" t="n">
-        <v>46246</v>
-      </c>
-      <c r="H33" s="25" t="n">
-        <v>46270</v>
-      </c>
+      <c r="A33" s="23" t="n"/>
+      <c r="B33" s="23" t="n"/>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="23" t="n"/>
+      <c r="E33" s="23" t="n"/>
+      <c r="F33" s="24" t="n"/>
+      <c r="G33" s="25" t="n"/>
+      <c r="H33" s="25" t="n"/>
       <c r="I33" s="26">
         <f>IF(E33="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E33,PARAMETER!$B$9:$B$14,0)),0))</f>
         <v/>
@@ -2682,40 +2506,14 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="23" t="inlineStr">
-        <is>
-          <t>D-029</t>
-        </is>
-      </c>
-      <c r="B34" s="23" t="inlineStr">
-        <is>
-          <t>CV Tunas Harapan</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="inlineStr">
-        <is>
-          <t>Sekar Wulandari</t>
-        </is>
-      </c>
-      <c r="D34" s="23" t="inlineStr">
-        <is>
-          <t>Media Sosial</t>
-        </is>
-      </c>
-      <c r="E34" s="23" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="F34" s="24" t="n">
-        <v>23000000</v>
-      </c>
-      <c r="G34" s="25" t="n">
-        <v>46129</v>
-      </c>
-      <c r="H34" s="25" t="n">
-        <v>46431</v>
-      </c>
+      <c r="A34" s="23" t="n"/>
+      <c r="B34" s="23" t="n"/>
+      <c r="C34" s="23" t="n"/>
+      <c r="D34" s="23" t="n"/>
+      <c r="E34" s="23" t="n"/>
+      <c r="F34" s="24" t="n"/>
+      <c r="G34" s="25" t="n"/>
+      <c r="H34" s="25" t="n"/>
       <c r="I34" s="26">
         <f>IF(E34="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E34,PARAMETER!$B$9:$B$14,0)),0))</f>
         <v/>
@@ -2734,40 +2532,14 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="23" t="inlineStr">
-        <is>
-          <t>D-030</t>
-        </is>
-      </c>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>PT Mega Pangan</t>
-        </is>
-      </c>
-      <c r="C35" s="23" t="inlineStr">
-        <is>
-          <t>Sekar Wulandari</t>
-        </is>
-      </c>
-      <c r="D35" s="23" t="inlineStr">
-        <is>
-          <t>Cold Call</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="inlineStr">
-        <is>
-          <t>Menang</t>
-        </is>
-      </c>
-      <c r="F35" s="24" t="n">
-        <v>122000000</v>
-      </c>
-      <c r="G35" s="25" t="n">
-        <v>46229</v>
-      </c>
-      <c r="H35" s="25" t="n">
-        <v>46280</v>
-      </c>
+      <c r="A35" s="23" t="n"/>
+      <c r="B35" s="23" t="n"/>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="23" t="n"/>
+      <c r="F35" s="24" t="n"/>
+      <c r="G35" s="25" t="n"/>
+      <c r="H35" s="25" t="n"/>
       <c r="I35" s="26">
         <f>IF(E35="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E35,PARAMETER!$B$9:$B$14,0)),0))</f>
         <v/>
@@ -2785,1053 +2557,13 @@
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t>D-031</t>
-        </is>
-      </c>
-      <c r="B36" s="23" t="inlineStr">
-        <is>
-          <t>CV Berkah Sentosa</t>
-        </is>
-      </c>
-      <c r="C36" s="23" t="inlineStr">
-        <is>
-          <t>Sekar Wulandari</t>
-        </is>
-      </c>
-      <c r="D36" s="23" t="inlineStr">
-        <is>
-          <t>Mitra</t>
-        </is>
-      </c>
-      <c r="E36" s="23" t="inlineStr">
-        <is>
-          <t>Menang</t>
-        </is>
-      </c>
-      <c r="F36" s="24" t="n">
-        <v>59000000</v>
-      </c>
-      <c r="G36" s="25" t="n">
-        <v>46169</v>
-      </c>
-      <c r="H36" s="25" t="n">
-        <v>46202</v>
-      </c>
-      <c r="I36" s="26">
-        <f>IF(E36="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E36,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J36" s="27">
-        <f>IF(OR(F36="",I36=""),"",F36*I36)</f>
-        <v/>
-      </c>
-      <c r="K36" s="28">
-        <f>IF(OR(E36="",G36=""),"",IF(OR(E36="Menang",E36="Kalah"),"",PARAMETER!$C$5-G36))</f>
-        <v/>
-      </c>
-      <c r="L36" s="29">
-        <f>IF(E36="","",IF(OR(E36="Menang",E36="Kalah"),E36,IF(H36&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="23" t="inlineStr">
-        <is>
-          <t>D-032</t>
-        </is>
-      </c>
-      <c r="B37" s="23" t="inlineStr">
-        <is>
-          <t>PT Samudra Niaga</t>
-        </is>
-      </c>
-      <c r="C37" s="23" t="inlineStr">
-        <is>
-          <t>Sekar Wulandari</t>
-        </is>
-      </c>
-      <c r="D37" s="23" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="F37" s="24" t="n">
-        <v>165000000</v>
-      </c>
-      <c r="G37" s="25" t="n">
-        <v>46147</v>
-      </c>
-      <c r="H37" s="25" t="n">
-        <v>46436</v>
-      </c>
-      <c r="I37" s="26">
-        <f>IF(E37="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E37,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J37" s="27">
-        <f>IF(OR(F37="",I37=""),"",F37*I37)</f>
-        <v/>
-      </c>
-      <c r="K37" s="28">
-        <f>IF(OR(E37="",G37=""),"",IF(OR(E37="Menang",E37="Kalah"),"",PARAMETER!$C$5-G37))</f>
-        <v/>
-      </c>
-      <c r="L37" s="29">
-        <f>IF(E37="","",IF(OR(E37="Menang",E37="Kalah"),E37,IF(H37&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="23" t="inlineStr">
-        <is>
-          <t>D-033</t>
-        </is>
-      </c>
-      <c r="B38" s="23" t="inlineStr">
-        <is>
-          <t>PT Karya Mandiri</t>
-        </is>
-      </c>
-      <c r="C38" s="23" t="inlineStr">
-        <is>
-          <t>Dimas Anggoro</t>
-        </is>
-      </c>
-      <c r="D38" s="23" t="inlineStr">
-        <is>
-          <t>Media Sosial</t>
-        </is>
-      </c>
-      <c r="E38" s="23" t="inlineStr">
-        <is>
-          <t>Kualifikasi</t>
-        </is>
-      </c>
-      <c r="F38" s="24" t="n">
-        <v>71000000</v>
-      </c>
-      <c r="G38" s="25" t="n">
-        <v>46108</v>
-      </c>
-      <c r="H38" s="25" t="n">
-        <v>46396</v>
-      </c>
-      <c r="I38" s="26">
-        <f>IF(E38="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E38,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J38" s="27">
-        <f>IF(OR(F38="",I38=""),"",F38*I38)</f>
-        <v/>
-      </c>
-      <c r="K38" s="28">
-        <f>IF(OR(E38="",G38=""),"",IF(OR(E38="Menang",E38="Kalah"),"",PARAMETER!$C$5-G38))</f>
-        <v/>
-      </c>
-      <c r="L38" s="29">
-        <f>IF(E38="","",IF(OR(E38="Menang",E38="Kalah"),E38,IF(H38&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="23" t="inlineStr">
-        <is>
-          <t>D-034</t>
-        </is>
-      </c>
-      <c r="B39" s="23" t="inlineStr">
-        <is>
-          <t>PT Cahaya Prima</t>
-        </is>
-      </c>
-      <c r="C39" s="23" t="inlineStr">
-        <is>
-          <t>Dimas Anggoro</t>
-        </is>
-      </c>
-      <c r="D39" s="23" t="inlineStr">
-        <is>
-          <t>Pameran</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="inlineStr">
-        <is>
-          <t>Kalah</t>
-        </is>
-      </c>
-      <c r="F39" s="24" t="n">
-        <v>87000000</v>
-      </c>
-      <c r="G39" s="25" t="n">
-        <v>46237</v>
-      </c>
-      <c r="H39" s="25" t="n">
-        <v>46287</v>
-      </c>
-      <c r="I39" s="26">
-        <f>IF(E39="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E39,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J39" s="27">
-        <f>IF(OR(F39="",I39=""),"",F39*I39)</f>
-        <v/>
-      </c>
-      <c r="K39" s="28">
-        <f>IF(OR(E39="",G39=""),"",IF(OR(E39="Menang",E39="Kalah"),"",PARAMETER!$C$5-G39))</f>
-        <v/>
-      </c>
-      <c r="L39" s="29">
-        <f>IF(E39="","",IF(OR(E39="Menang",E39="Kalah"),E39,IF(H39&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="23" t="inlineStr">
-        <is>
-          <t>D-035</t>
-        </is>
-      </c>
-      <c r="B40" s="23" t="inlineStr">
-        <is>
-          <t>PT Mega Pangan</t>
-        </is>
-      </c>
-      <c r="C40" s="23" t="inlineStr">
-        <is>
-          <t>Sekar Wulandari</t>
-        </is>
-      </c>
-      <c r="D40" s="23" t="inlineStr">
-        <is>
-          <t>Cold Call</t>
-        </is>
-      </c>
-      <c r="E40" s="23" t="inlineStr">
-        <is>
-          <t>Kualifikasi</t>
-        </is>
-      </c>
-      <c r="F40" s="24" t="n">
-        <v>90000000</v>
-      </c>
-      <c r="G40" s="25" t="n">
-        <v>46309</v>
-      </c>
-      <c r="H40" s="25" t="n">
-        <v>46418</v>
-      </c>
-      <c r="I40" s="26">
-        <f>IF(E40="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E40,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J40" s="27">
-        <f>IF(OR(F40="",I40=""),"",F40*I40)</f>
-        <v/>
-      </c>
-      <c r="K40" s="28">
-        <f>IF(OR(E40="",G40=""),"",IF(OR(E40="Menang",E40="Kalah"),"",PARAMETER!$C$5-G40))</f>
-        <v/>
-      </c>
-      <c r="L40" s="29">
-        <f>IF(E40="","",IF(OR(E40="Menang",E40="Kalah"),E40,IF(H40&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="23" t="inlineStr">
-        <is>
-          <t>D-036</t>
-        </is>
-      </c>
-      <c r="B41" s="23" t="inlineStr">
-        <is>
-          <t>PT Indo Sejahtera</t>
-        </is>
-      </c>
-      <c r="C41" s="23" t="inlineStr">
-        <is>
-          <t>Dimas Anggoro</t>
-        </is>
-      </c>
-      <c r="D41" s="23" t="inlineStr">
-        <is>
-          <t>Cold Call</t>
-        </is>
-      </c>
-      <c r="E41" s="23" t="inlineStr">
-        <is>
-          <t>Kalah</t>
-        </is>
-      </c>
-      <c r="F41" s="24" t="n">
-        <v>27000000</v>
-      </c>
-      <c r="G41" s="25" t="n">
-        <v>46106</v>
-      </c>
-      <c r="H41" s="25" t="n">
-        <v>46148</v>
-      </c>
-      <c r="I41" s="26">
-        <f>IF(E41="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E41,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J41" s="27">
-        <f>IF(OR(F41="",I41=""),"",F41*I41)</f>
-        <v/>
-      </c>
-      <c r="K41" s="28">
-        <f>IF(OR(E41="",G41=""),"",IF(OR(E41="Menang",E41="Kalah"),"",PARAMETER!$C$5-G41))</f>
-        <v/>
-      </c>
-      <c r="L41" s="29">
-        <f>IF(E41="","",IF(OR(E41="Menang",E41="Kalah"),E41,IF(H41&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="23" t="inlineStr">
-        <is>
-          <t>D-037</t>
-        </is>
-      </c>
-      <c r="B42" s="23" t="inlineStr">
-        <is>
-          <t>PT Arta Makmur</t>
-        </is>
-      </c>
-      <c r="C42" s="23" t="inlineStr">
-        <is>
-          <t>Rina Pratama</t>
-        </is>
-      </c>
-      <c r="D42" s="23" t="inlineStr">
-        <is>
-          <t>Media Sosial</t>
-        </is>
-      </c>
-      <c r="E42" s="23" t="inlineStr">
-        <is>
-          <t>Kalah</t>
-        </is>
-      </c>
-      <c r="F42" s="24" t="n">
-        <v>208000000</v>
-      </c>
-      <c r="G42" s="25" t="n">
-        <v>46213</v>
-      </c>
-      <c r="H42" s="25" t="n">
-        <v>46272</v>
-      </c>
-      <c r="I42" s="26">
-        <f>IF(E42="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E42,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J42" s="27">
-        <f>IF(OR(F42="",I42=""),"",F42*I42)</f>
-        <v/>
-      </c>
-      <c r="K42" s="28">
-        <f>IF(OR(E42="",G42=""),"",IF(OR(E42="Menang",E42="Kalah"),"",PARAMETER!$C$5-G42))</f>
-        <v/>
-      </c>
-      <c r="L42" s="29">
-        <f>IF(E42="","",IF(OR(E42="Menang",E42="Kalah"),E42,IF(H42&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="23" t="inlineStr">
-        <is>
-          <t>D-038</t>
-        </is>
-      </c>
-      <c r="B43" s="23" t="inlineStr">
-        <is>
-          <t>PT Nusantara Jaya</t>
-        </is>
-      </c>
-      <c r="C43" s="23" t="inlineStr">
-        <is>
-          <t>Sekar Wulandari</t>
-        </is>
-      </c>
-      <c r="D43" s="23" t="inlineStr">
-        <is>
-          <t>Referral</t>
-        </is>
-      </c>
-      <c r="E43" s="23" t="inlineStr">
-        <is>
-          <t>Kualifikasi</t>
-        </is>
-      </c>
-      <c r="F43" s="24" t="n">
-        <v>268000000</v>
-      </c>
-      <c r="G43" s="25" t="n">
-        <v>46239</v>
-      </c>
-      <c r="H43" s="25" t="n">
-        <v>46421</v>
-      </c>
-      <c r="I43" s="26">
-        <f>IF(E43="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E43,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J43" s="27">
-        <f>IF(OR(F43="",I43=""),"",F43*I43)</f>
-        <v/>
-      </c>
-      <c r="K43" s="28">
-        <f>IF(OR(E43="",G43=""),"",IF(OR(E43="Menang",E43="Kalah"),"",PARAMETER!$C$5-G43))</f>
-        <v/>
-      </c>
-      <c r="L43" s="29">
-        <f>IF(E43="","",IF(OR(E43="Menang",E43="Kalah"),E43,IF(H43&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="23" t="inlineStr">
-        <is>
-          <t>D-039</t>
-        </is>
-      </c>
-      <c r="B44" s="23" t="inlineStr">
-        <is>
-          <t>PT Samudra Niaga</t>
-        </is>
-      </c>
-      <c r="C44" s="23" t="inlineStr">
-        <is>
-          <t>Dimas Anggoro</t>
-        </is>
-      </c>
-      <c r="D44" s="23" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="E44" s="23" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="F44" s="24" t="n">
-        <v>90000000</v>
-      </c>
-      <c r="G44" s="25" t="n">
-        <v>46216</v>
-      </c>
-      <c r="H44" s="25" t="n">
-        <v>46336</v>
-      </c>
-      <c r="I44" s="26">
-        <f>IF(E44="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E44,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J44" s="27">
-        <f>IF(OR(F44="",I44=""),"",F44*I44)</f>
-        <v/>
-      </c>
-      <c r="K44" s="28">
-        <f>IF(OR(E44="",G44=""),"",IF(OR(E44="Menang",E44="Kalah"),"",PARAMETER!$C$5-G44))</f>
-        <v/>
-      </c>
-      <c r="L44" s="29">
-        <f>IF(E44="","",IF(OR(E44="Menang",E44="Kalah"),E44,IF(H44&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="23" t="inlineStr">
-        <is>
-          <t>D-040</t>
-        </is>
-      </c>
-      <c r="B45" s="23" t="inlineStr">
-        <is>
-          <t>CV Berkah Sentosa</t>
-        </is>
-      </c>
-      <c r="C45" s="23" t="inlineStr">
-        <is>
-          <t>Dimas Anggoro</t>
-        </is>
-      </c>
-      <c r="D45" s="23" t="inlineStr">
-        <is>
-          <t>Pameran</t>
-        </is>
-      </c>
-      <c r="E45" s="23" t="inlineStr">
-        <is>
-          <t>Prospek</t>
-        </is>
-      </c>
-      <c r="F45" s="24" t="n">
-        <v>36000000</v>
-      </c>
-      <c r="G45" s="25" t="n">
-        <v>46133</v>
-      </c>
-      <c r="H45" s="25" t="n">
-        <v>46434</v>
-      </c>
-      <c r="I45" s="26">
-        <f>IF(E45="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E45,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J45" s="27">
-        <f>IF(OR(F45="",I45=""),"",F45*I45)</f>
-        <v/>
-      </c>
-      <c r="K45" s="28">
-        <f>IF(OR(E45="",G45=""),"",IF(OR(E45="Menang",E45="Kalah"),"",PARAMETER!$C$5-G45))</f>
-        <v/>
-      </c>
-      <c r="L45" s="29">
-        <f>IF(E45="","",IF(OR(E45="Menang",E45="Kalah"),E45,IF(H45&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="23" t="n"/>
-      <c r="B46" s="23" t="n"/>
-      <c r="C46" s="23" t="n"/>
-      <c r="D46" s="23" t="n"/>
-      <c r="E46" s="23" t="n"/>
-      <c r="F46" s="24" t="n"/>
-      <c r="G46" s="25" t="n"/>
-      <c r="H46" s="25" t="n"/>
-      <c r="I46" s="26">
-        <f>IF(E46="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E46,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J46" s="27">
-        <f>IF(OR(F46="",I46=""),"",F46*I46)</f>
-        <v/>
-      </c>
-      <c r="K46" s="28">
-        <f>IF(OR(E46="",G46=""),"",IF(OR(E46="Menang",E46="Kalah"),"",PARAMETER!$C$5-G46))</f>
-        <v/>
-      </c>
-      <c r="L46" s="29">
-        <f>IF(E46="","",IF(OR(E46="Menang",E46="Kalah"),E46,IF(H46&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="23" t="n"/>
-      <c r="B47" s="23" t="n"/>
-      <c r="C47" s="23" t="n"/>
-      <c r="D47" s="23" t="n"/>
-      <c r="E47" s="23" t="n"/>
-      <c r="F47" s="24" t="n"/>
-      <c r="G47" s="25" t="n"/>
-      <c r="H47" s="25" t="n"/>
-      <c r="I47" s="26">
-        <f>IF(E47="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E47,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J47" s="27">
-        <f>IF(OR(F47="",I47=""),"",F47*I47)</f>
-        <v/>
-      </c>
-      <c r="K47" s="28">
-        <f>IF(OR(E47="",G47=""),"",IF(OR(E47="Menang",E47="Kalah"),"",PARAMETER!$C$5-G47))</f>
-        <v/>
-      </c>
-      <c r="L47" s="29">
-        <f>IF(E47="","",IF(OR(E47="Menang",E47="Kalah"),E47,IF(H47&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="23" t="n"/>
-      <c r="B48" s="23" t="n"/>
-      <c r="C48" s="23" t="n"/>
-      <c r="D48" s="23" t="n"/>
-      <c r="E48" s="23" t="n"/>
-      <c r="F48" s="24" t="n"/>
-      <c r="G48" s="25" t="n"/>
-      <c r="H48" s="25" t="n"/>
-      <c r="I48" s="26">
-        <f>IF(E48="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E48,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J48" s="27">
-        <f>IF(OR(F48="",I48=""),"",F48*I48)</f>
-        <v/>
-      </c>
-      <c r="K48" s="28">
-        <f>IF(OR(E48="",G48=""),"",IF(OR(E48="Menang",E48="Kalah"),"",PARAMETER!$C$5-G48))</f>
-        <v/>
-      </c>
-      <c r="L48" s="29">
-        <f>IF(E48="","",IF(OR(E48="Menang",E48="Kalah"),E48,IF(H48&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="23" t="n"/>
-      <c r="B49" s="23" t="n"/>
-      <c r="C49" s="23" t="n"/>
-      <c r="D49" s="23" t="n"/>
-      <c r="E49" s="23" t="n"/>
-      <c r="F49" s="24" t="n"/>
-      <c r="G49" s="25" t="n"/>
-      <c r="H49" s="25" t="n"/>
-      <c r="I49" s="26">
-        <f>IF(E49="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E49,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J49" s="27">
-        <f>IF(OR(F49="",I49=""),"",F49*I49)</f>
-        <v/>
-      </c>
-      <c r="K49" s="28">
-        <f>IF(OR(E49="",G49=""),"",IF(OR(E49="Menang",E49="Kalah"),"",PARAMETER!$C$5-G49))</f>
-        <v/>
-      </c>
-      <c r="L49" s="29">
-        <f>IF(E49="","",IF(OR(E49="Menang",E49="Kalah"),E49,IF(H49&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="23" t="n"/>
-      <c r="B50" s="23" t="n"/>
-      <c r="C50" s="23" t="n"/>
-      <c r="D50" s="23" t="n"/>
-      <c r="E50" s="23" t="n"/>
-      <c r="F50" s="24" t="n"/>
-      <c r="G50" s="25" t="n"/>
-      <c r="H50" s="25" t="n"/>
-      <c r="I50" s="26">
-        <f>IF(E50="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E50,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J50" s="27">
-        <f>IF(OR(F50="",I50=""),"",F50*I50)</f>
-        <v/>
-      </c>
-      <c r="K50" s="28">
-        <f>IF(OR(E50="",G50=""),"",IF(OR(E50="Menang",E50="Kalah"),"",PARAMETER!$C$5-G50))</f>
-        <v/>
-      </c>
-      <c r="L50" s="29">
-        <f>IF(E50="","",IF(OR(E50="Menang",E50="Kalah"),E50,IF(H50&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="23" t="n"/>
-      <c r="B51" s="23" t="n"/>
-      <c r="C51" s="23" t="n"/>
-      <c r="D51" s="23" t="n"/>
-      <c r="E51" s="23" t="n"/>
-      <c r="F51" s="24" t="n"/>
-      <c r="G51" s="25" t="n"/>
-      <c r="H51" s="25" t="n"/>
-      <c r="I51" s="26">
-        <f>IF(E51="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E51,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J51" s="27">
-        <f>IF(OR(F51="",I51=""),"",F51*I51)</f>
-        <v/>
-      </c>
-      <c r="K51" s="28">
-        <f>IF(OR(E51="",G51=""),"",IF(OR(E51="Menang",E51="Kalah"),"",PARAMETER!$C$5-G51))</f>
-        <v/>
-      </c>
-      <c r="L51" s="29">
-        <f>IF(E51="","",IF(OR(E51="Menang",E51="Kalah"),E51,IF(H51&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="23" t="n"/>
-      <c r="B52" s="23" t="n"/>
-      <c r="C52" s="23" t="n"/>
-      <c r="D52" s="23" t="n"/>
-      <c r="E52" s="23" t="n"/>
-      <c r="F52" s="24" t="n"/>
-      <c r="G52" s="25" t="n"/>
-      <c r="H52" s="25" t="n"/>
-      <c r="I52" s="26">
-        <f>IF(E52="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E52,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J52" s="27">
-        <f>IF(OR(F52="",I52=""),"",F52*I52)</f>
-        <v/>
-      </c>
-      <c r="K52" s="28">
-        <f>IF(OR(E52="",G52=""),"",IF(OR(E52="Menang",E52="Kalah"),"",PARAMETER!$C$5-G52))</f>
-        <v/>
-      </c>
-      <c r="L52" s="29">
-        <f>IF(E52="","",IF(OR(E52="Menang",E52="Kalah"),E52,IF(H52&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="23" t="n"/>
-      <c r="B53" s="23" t="n"/>
-      <c r="C53" s="23" t="n"/>
-      <c r="D53" s="23" t="n"/>
-      <c r="E53" s="23" t="n"/>
-      <c r="F53" s="24" t="n"/>
-      <c r="G53" s="25" t="n"/>
-      <c r="H53" s="25" t="n"/>
-      <c r="I53" s="26">
-        <f>IF(E53="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E53,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J53" s="27">
-        <f>IF(OR(F53="",I53=""),"",F53*I53)</f>
-        <v/>
-      </c>
-      <c r="K53" s="28">
-        <f>IF(OR(E53="",G53=""),"",IF(OR(E53="Menang",E53="Kalah"),"",PARAMETER!$C$5-G53))</f>
-        <v/>
-      </c>
-      <c r="L53" s="29">
-        <f>IF(E53="","",IF(OR(E53="Menang",E53="Kalah"),E53,IF(H53&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="23" t="n"/>
-      <c r="B54" s="23" t="n"/>
-      <c r="C54" s="23" t="n"/>
-      <c r="D54" s="23" t="n"/>
-      <c r="E54" s="23" t="n"/>
-      <c r="F54" s="24" t="n"/>
-      <c r="G54" s="25" t="n"/>
-      <c r="H54" s="25" t="n"/>
-      <c r="I54" s="26">
-        <f>IF(E54="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E54,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J54" s="27">
-        <f>IF(OR(F54="",I54=""),"",F54*I54)</f>
-        <v/>
-      </c>
-      <c r="K54" s="28">
-        <f>IF(OR(E54="",G54=""),"",IF(OR(E54="Menang",E54="Kalah"),"",PARAMETER!$C$5-G54))</f>
-        <v/>
-      </c>
-      <c r="L54" s="29">
-        <f>IF(E54="","",IF(OR(E54="Menang",E54="Kalah"),E54,IF(H54&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="23" t="n"/>
-      <c r="B55" s="23" t="n"/>
-      <c r="C55" s="23" t="n"/>
-      <c r="D55" s="23" t="n"/>
-      <c r="E55" s="23" t="n"/>
-      <c r="F55" s="24" t="n"/>
-      <c r="G55" s="25" t="n"/>
-      <c r="H55" s="25" t="n"/>
-      <c r="I55" s="26">
-        <f>IF(E55="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E55,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J55" s="27">
-        <f>IF(OR(F55="",I55=""),"",F55*I55)</f>
-        <v/>
-      </c>
-      <c r="K55" s="28">
-        <f>IF(OR(E55="",G55=""),"",IF(OR(E55="Menang",E55="Kalah"),"",PARAMETER!$C$5-G55))</f>
-        <v/>
-      </c>
-      <c r="L55" s="29">
-        <f>IF(E55="","",IF(OR(E55="Menang",E55="Kalah"),E55,IF(H55&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="23" t="n"/>
-      <c r="B56" s="23" t="n"/>
-      <c r="C56" s="23" t="n"/>
-      <c r="D56" s="23" t="n"/>
-      <c r="E56" s="23" t="n"/>
-      <c r="F56" s="24" t="n"/>
-      <c r="G56" s="25" t="n"/>
-      <c r="H56" s="25" t="n"/>
-      <c r="I56" s="26">
-        <f>IF(E56="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E56,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J56" s="27">
-        <f>IF(OR(F56="",I56=""),"",F56*I56)</f>
-        <v/>
-      </c>
-      <c r="K56" s="28">
-        <f>IF(OR(E56="",G56=""),"",IF(OR(E56="Menang",E56="Kalah"),"",PARAMETER!$C$5-G56))</f>
-        <v/>
-      </c>
-      <c r="L56" s="29">
-        <f>IF(E56="","",IF(OR(E56="Menang",E56="Kalah"),E56,IF(H56&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="23" t="n"/>
-      <c r="B57" s="23" t="n"/>
-      <c r="C57" s="23" t="n"/>
-      <c r="D57" s="23" t="n"/>
-      <c r="E57" s="23" t="n"/>
-      <c r="F57" s="24" t="n"/>
-      <c r="G57" s="25" t="n"/>
-      <c r="H57" s="25" t="n"/>
-      <c r="I57" s="26">
-        <f>IF(E57="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E57,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J57" s="27">
-        <f>IF(OR(F57="",I57=""),"",F57*I57)</f>
-        <v/>
-      </c>
-      <c r="K57" s="28">
-        <f>IF(OR(E57="",G57=""),"",IF(OR(E57="Menang",E57="Kalah"),"",PARAMETER!$C$5-G57))</f>
-        <v/>
-      </c>
-      <c r="L57" s="29">
-        <f>IF(E57="","",IF(OR(E57="Menang",E57="Kalah"),E57,IF(H57&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="23" t="n"/>
-      <c r="B58" s="23" t="n"/>
-      <c r="C58" s="23" t="n"/>
-      <c r="D58" s="23" t="n"/>
-      <c r="E58" s="23" t="n"/>
-      <c r="F58" s="24" t="n"/>
-      <c r="G58" s="25" t="n"/>
-      <c r="H58" s="25" t="n"/>
-      <c r="I58" s="26">
-        <f>IF(E58="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E58,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J58" s="27">
-        <f>IF(OR(F58="",I58=""),"",F58*I58)</f>
-        <v/>
-      </c>
-      <c r="K58" s="28">
-        <f>IF(OR(E58="",G58=""),"",IF(OR(E58="Menang",E58="Kalah"),"",PARAMETER!$C$5-G58))</f>
-        <v/>
-      </c>
-      <c r="L58" s="29">
-        <f>IF(E58="","",IF(OR(E58="Menang",E58="Kalah"),E58,IF(H58&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="23" t="n"/>
-      <c r="B59" s="23" t="n"/>
-      <c r="C59" s="23" t="n"/>
-      <c r="D59" s="23" t="n"/>
-      <c r="E59" s="23" t="n"/>
-      <c r="F59" s="24" t="n"/>
-      <c r="G59" s="25" t="n"/>
-      <c r="H59" s="25" t="n"/>
-      <c r="I59" s="26">
-        <f>IF(E59="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E59,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J59" s="27">
-        <f>IF(OR(F59="",I59=""),"",F59*I59)</f>
-        <v/>
-      </c>
-      <c r="K59" s="28">
-        <f>IF(OR(E59="",G59=""),"",IF(OR(E59="Menang",E59="Kalah"),"",PARAMETER!$C$5-G59))</f>
-        <v/>
-      </c>
-      <c r="L59" s="29">
-        <f>IF(E59="","",IF(OR(E59="Menang",E59="Kalah"),E59,IF(H59&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="23" t="n"/>
-      <c r="B60" s="23" t="n"/>
-      <c r="C60" s="23" t="n"/>
-      <c r="D60" s="23" t="n"/>
-      <c r="E60" s="23" t="n"/>
-      <c r="F60" s="24" t="n"/>
-      <c r="G60" s="25" t="n"/>
-      <c r="H60" s="25" t="n"/>
-      <c r="I60" s="26">
-        <f>IF(E60="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E60,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J60" s="27">
-        <f>IF(OR(F60="",I60=""),"",F60*I60)</f>
-        <v/>
-      </c>
-      <c r="K60" s="28">
-        <f>IF(OR(E60="",G60=""),"",IF(OR(E60="Menang",E60="Kalah"),"",PARAMETER!$C$5-G60))</f>
-        <v/>
-      </c>
-      <c r="L60" s="29">
-        <f>IF(E60="","",IF(OR(E60="Menang",E60="Kalah"),E60,IF(H60&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="23" t="n"/>
-      <c r="B61" s="23" t="n"/>
-      <c r="C61" s="23" t="n"/>
-      <c r="D61" s="23" t="n"/>
-      <c r="E61" s="23" t="n"/>
-      <c r="F61" s="24" t="n"/>
-      <c r="G61" s="25" t="n"/>
-      <c r="H61" s="25" t="n"/>
-      <c r="I61" s="26">
-        <f>IF(E61="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E61,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J61" s="27">
-        <f>IF(OR(F61="",I61=""),"",F61*I61)</f>
-        <v/>
-      </c>
-      <c r="K61" s="28">
-        <f>IF(OR(E61="",G61=""),"",IF(OR(E61="Menang",E61="Kalah"),"",PARAMETER!$C$5-G61))</f>
-        <v/>
-      </c>
-      <c r="L61" s="29">
-        <f>IF(E61="","",IF(OR(E61="Menang",E61="Kalah"),E61,IF(H61&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="23" t="n"/>
-      <c r="B62" s="23" t="n"/>
-      <c r="C62" s="23" t="n"/>
-      <c r="D62" s="23" t="n"/>
-      <c r="E62" s="23" t="n"/>
-      <c r="F62" s="24" t="n"/>
-      <c r="G62" s="25" t="n"/>
-      <c r="H62" s="25" t="n"/>
-      <c r="I62" s="26">
-        <f>IF(E62="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E62,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J62" s="27">
-        <f>IF(OR(F62="",I62=""),"",F62*I62)</f>
-        <v/>
-      </c>
-      <c r="K62" s="28">
-        <f>IF(OR(E62="",G62=""),"",IF(OR(E62="Menang",E62="Kalah"),"",PARAMETER!$C$5-G62))</f>
-        <v/>
-      </c>
-      <c r="L62" s="29">
-        <f>IF(E62="","",IF(OR(E62="Menang",E62="Kalah"),E62,IF(H62&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="23" t="n"/>
-      <c r="B63" s="23" t="n"/>
-      <c r="C63" s="23" t="n"/>
-      <c r="D63" s="23" t="n"/>
-      <c r="E63" s="23" t="n"/>
-      <c r="F63" s="24" t="n"/>
-      <c r="G63" s="25" t="n"/>
-      <c r="H63" s="25" t="n"/>
-      <c r="I63" s="26">
-        <f>IF(E63="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E63,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J63" s="27">
-        <f>IF(OR(F63="",I63=""),"",F63*I63)</f>
-        <v/>
-      </c>
-      <c r="K63" s="28">
-        <f>IF(OR(E63="",G63=""),"",IF(OR(E63="Menang",E63="Kalah"),"",PARAMETER!$C$5-G63))</f>
-        <v/>
-      </c>
-      <c r="L63" s="29">
-        <f>IF(E63="","",IF(OR(E63="Menang",E63="Kalah"),E63,IF(H63&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="23" t="n"/>
-      <c r="B64" s="23" t="n"/>
-      <c r="C64" s="23" t="n"/>
-      <c r="D64" s="23" t="n"/>
-      <c r="E64" s="23" t="n"/>
-      <c r="F64" s="24" t="n"/>
-      <c r="G64" s="25" t="n"/>
-      <c r="H64" s="25" t="n"/>
-      <c r="I64" s="26">
-        <f>IF(E64="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E64,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J64" s="27">
-        <f>IF(OR(F64="",I64=""),"",F64*I64)</f>
-        <v/>
-      </c>
-      <c r="K64" s="28">
-        <f>IF(OR(E64="",G64=""),"",IF(OR(E64="Menang",E64="Kalah"),"",PARAMETER!$C$5-G64))</f>
-        <v/>
-      </c>
-      <c r="L64" s="29">
-        <f>IF(E64="","",IF(OR(E64="Menang",E64="Kalah"),E64,IF(H64&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="23" t="n"/>
-      <c r="B65" s="23" t="n"/>
-      <c r="C65" s="23" t="n"/>
-      <c r="D65" s="23" t="n"/>
-      <c r="E65" s="23" t="n"/>
-      <c r="F65" s="24" t="n"/>
-      <c r="G65" s="25" t="n"/>
-      <c r="H65" s="25" t="n"/>
-      <c r="I65" s="26">
-        <f>IF(E65="","",IFERROR(INDEX(PARAMETER!$C$9:$C$14,MATCH(E65,PARAMETER!$B$9:$B$14,0)),0))</f>
-        <v/>
-      </c>
-      <c r="J65" s="27">
-        <f>IF(OR(F65="",I65=""),"",F65*I65)</f>
-        <v/>
-      </c>
-      <c r="K65" s="28">
-        <f>IF(OR(E65="",G65=""),"",IF(OR(E65="Menang",E65="Kalah"),"",PARAMETER!$C$5-G65))</f>
-        <v/>
-      </c>
-      <c r="L65" s="29">
-        <f>IF(E65="","",IF(OR(E65="Menang",E65="Kalah"),E65,IF(H65&lt;PARAMETER!$C$5,"Terlambat","Berjalan")))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <autoFilter ref="A5:L65"/>
+  <autoFilter ref="A5:L35"/>
   <mergeCells count="1">
     <mergeCell ref="A3:L3"/>
   </mergeCells>
-  <conditionalFormatting sqref="L6:L65">
+  <conditionalFormatting sqref="L6:L35">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Terlambat"</formula>
     </cfRule>
@@ -3840,13 +2572,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=PARAMETER!$B$17:$B$24</formula1>
     </dataValidation>
-    <dataValidation sqref="D6:D65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D6:D35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=PARAMETER!$D$17:$D$24</formula1>
     </dataValidation>
-    <dataValidation sqref="E6:E65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E6:E35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=PARAMETER!$B$9:$B$14</formula1>
     </dataValidation>
   </dataValidations>
@@ -3919,15 +2651,15 @@
         <v/>
       </c>
       <c r="B6" s="28">
-        <f>COUNTIFS(DEAL!$E$6:$E$65,A6)</f>
+        <f>COUNTIFS(DEAL!$E$6:$E$35,A6)</f>
         <v/>
       </c>
       <c r="C6" s="27">
-        <f>SUMIFS(DEAL!$F$6:$F$65,DEAL!$E$6:$E$65,A6)</f>
+        <f>SUMIFS(DEAL!$F$6:$F$35,DEAL!$E$6:$E$35,A6)</f>
         <v/>
       </c>
       <c r="D6" s="27">
-        <f>SUMIFS(DEAL!$J$6:$J$65,DEAL!$E$6:$E$65,A6)</f>
+        <f>SUMIFS(DEAL!$J$6:$J$35,DEAL!$E$6:$E$35,A6)</f>
         <v/>
       </c>
     </row>
@@ -3937,15 +2669,15 @@
         <v/>
       </c>
       <c r="B7" s="28">
-        <f>COUNTIFS(DEAL!$E$6:$E$65,A7)</f>
+        <f>COUNTIFS(DEAL!$E$6:$E$35,A7)</f>
         <v/>
       </c>
       <c r="C7" s="27">
-        <f>SUMIFS(DEAL!$F$6:$F$65,DEAL!$E$6:$E$65,A7)</f>
+        <f>SUMIFS(DEAL!$F$6:$F$35,DEAL!$E$6:$E$35,A7)</f>
         <v/>
       </c>
       <c r="D7" s="27">
-        <f>SUMIFS(DEAL!$J$6:$J$65,DEAL!$E$6:$E$65,A7)</f>
+        <f>SUMIFS(DEAL!$J$6:$J$35,DEAL!$E$6:$E$35,A7)</f>
         <v/>
       </c>
     </row>
@@ -3955,15 +2687,15 @@
         <v/>
       </c>
       <c r="B8" s="28">
-        <f>COUNTIFS(DEAL!$E$6:$E$65,A8)</f>
+        <f>COUNTIFS(DEAL!$E$6:$E$35,A8)</f>
         <v/>
       </c>
       <c r="C8" s="27">
-        <f>SUMIFS(DEAL!$F$6:$F$65,DEAL!$E$6:$E$65,A8)</f>
+        <f>SUMIFS(DEAL!$F$6:$F$35,DEAL!$E$6:$E$35,A8)</f>
         <v/>
       </c>
       <c r="D8" s="27">
-        <f>SUMIFS(DEAL!$J$6:$J$65,DEAL!$E$6:$E$65,A8)</f>
+        <f>SUMIFS(DEAL!$J$6:$J$35,DEAL!$E$6:$E$35,A8)</f>
         <v/>
       </c>
     </row>
@@ -3973,15 +2705,15 @@
         <v/>
       </c>
       <c r="B9" s="28">
-        <f>COUNTIFS(DEAL!$E$6:$E$65,A9)</f>
+        <f>COUNTIFS(DEAL!$E$6:$E$35,A9)</f>
         <v/>
       </c>
       <c r="C9" s="27">
-        <f>SUMIFS(DEAL!$F$6:$F$65,DEAL!$E$6:$E$65,A9)</f>
+        <f>SUMIFS(DEAL!$F$6:$F$35,DEAL!$E$6:$E$35,A9)</f>
         <v/>
       </c>
       <c r="D9" s="27">
-        <f>SUMIFS(DEAL!$J$6:$J$65,DEAL!$E$6:$E$65,A9)</f>
+        <f>SUMIFS(DEAL!$J$6:$J$35,DEAL!$E$6:$E$35,A9)</f>
         <v/>
       </c>
     </row>
@@ -3991,15 +2723,15 @@
         <v/>
       </c>
       <c r="B10" s="28">
-        <f>COUNTIFS(DEAL!$E$6:$E$65,A10)</f>
+        <f>COUNTIFS(DEAL!$E$6:$E$35,A10)</f>
         <v/>
       </c>
       <c r="C10" s="27">
-        <f>SUMIFS(DEAL!$F$6:$F$65,DEAL!$E$6:$E$65,A10)</f>
+        <f>SUMIFS(DEAL!$F$6:$F$35,DEAL!$E$6:$E$35,A10)</f>
         <v/>
       </c>
       <c r="D10" s="27">
-        <f>SUMIFS(DEAL!$J$6:$J$65,DEAL!$E$6:$E$65,A10)</f>
+        <f>SUMIFS(DEAL!$J$6:$J$35,DEAL!$E$6:$E$35,A10)</f>
         <v/>
       </c>
     </row>
@@ -4009,15 +2741,15 @@
         <v/>
       </c>
       <c r="B11" s="28">
-        <f>COUNTIFS(DEAL!$E$6:$E$65,A11)</f>
+        <f>COUNTIFS(DEAL!$E$6:$E$35,A11)</f>
         <v/>
       </c>
       <c r="C11" s="27">
-        <f>SUMIFS(DEAL!$F$6:$F$65,DEAL!$E$6:$E$65,A11)</f>
+        <f>SUMIFS(DEAL!$F$6:$F$35,DEAL!$E$6:$E$35,A11)</f>
         <v/>
       </c>
       <c r="D11" s="27">
-        <f>SUMIFS(DEAL!$J$6:$J$65,DEAL!$E$6:$E$65,A11)</f>
+        <f>SUMIFS(DEAL!$J$6:$J$35,DEAL!$E$6:$E$35,A11)</f>
         <v/>
       </c>
     </row>
@@ -4123,7 +2855,7 @@
         </is>
       </c>
       <c r="B21" s="35">
-        <f>COUNTIFS(DEAL!$L$6:$L$65,"Terlambat")</f>
+        <f>COUNTIFS(DEAL!$L$6:$L$35,"Terlambat")</f>
         <v/>
       </c>
     </row>
@@ -4167,4 +2899,202 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C0392B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>Fitur Versi Lengkap</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>PER SALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Kinerja tiap sales: pipeline terbuka, tertimbang, nilai menang, win rate, capaian target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>• Sheet ini hanya tersedia di versi lengkap, lengkap dengan rumus dan grafik yang bekerja dari data Anda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>• Kapasitas data versi lengkap jauh lebih besar dibanding demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>• Pesan versi lengkap lewat WhatsApp 089623291732.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C0392B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>Fitur Versi Lengkap</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>FORECAST</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Prakiraan 6 bulan ke depan: Commit, Best Case, Tertimbang, plus deal yang lewat target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>• Sheet ini hanya tersedia di versi lengkap, lengkap dengan rumus dan grafik yang bekerja dari data Anda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>• Kapasitas data versi lengkap jauh lebih besar dibanding demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>• Pesan versi lengkap lewat WhatsApp 089623291732.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C0392B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>Fitur Versi Lengkap</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Grafik funnel per tahap dan prakiraan bulanan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>• Sheet ini hanya tersedia di versi lengkap, lengkap dengan rumus dan grafik yang bekerja dari data Anda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>• Kapasitas data versi lengkap jauh lebih besar dibanding demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>• Pesan versi lengkap lewat WhatsApp 089623291732.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>